--- a/model_maker_web_v2/results/Kstar/Kstar_stage1.xlsx
+++ b/model_maker_web_v2/results/Kstar/Kstar_stage1.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Kstar</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1_KSG1.250K.Inverter.Modbus.Communication.Protocol.3.5.pdf</t>
+          <t>Kstar_KSG1250K_Modbus_Protocol_v35.pdf</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-03 15:58</t>
+          <t>2026-04-03 16:03</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,11 @@
       </c>
       <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>2990=PV6 input power, 2991=04H, 2992=PV5 input volta, 2993=PV5 input curre, 2994=PV5 input power, 2995=04H... (+30)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
